--- a/community_mapping_photo_list.xlsx
+++ b/community_mapping_photo_list.xlsx
@@ -1,17 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AY CM code\anyang-community-map\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4644D5-5E85-44C0-B185-F0EFDE965A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="커뮤니티매핑_사진목록" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="참고사항" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="커뮤니티매핑_사진목록" sheetId="1" r:id="rId1"/>
+    <sheet name="참고사항" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -23,121 +28,117 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
   <si>
-    <t xml:space="preserve">연번</t>
-  </si>
-  <si>
-    <t xml:space="preserve">파일명</t>
-  </si>
-  <si>
-    <t xml:space="preserve">촬영일자</t>
-  </si>
-  <si>
-    <t xml:space="preserve">촬영시각</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
+    <t>연번</t>
+  </si>
+  <si>
+    <t>파일명</t>
+  </si>
+  <si>
+    <t>촬영일자</t>
+  </si>
+  <si>
+    <t>촬영시각</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">위도</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t>위도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(Lat)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Lat)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">경도</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t>경도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(Lng)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">방위각</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Lng)</t>
+    </r>
+  </si>
+  <si>
+    <t>방위각</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">주소</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t>주소</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">오버레이 텍스트</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t>오버레이 텍스트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">KakaoTalk_20260722_192143008.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86° E</t>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>KakaoTalk_20260722_192143008.jpg</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>18:53</t>
+  </si>
+  <si>
+    <t>86° E</t>
   </si>
   <si>
     <r>
@@ -152,20 +153,19 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1219-515</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">KakaoTalk_20260722_192143008_01.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">329° NW</t>
+        <family val="2"/>
+      </rPr>
+      <t>1219-515</t>
+    </r>
+  </si>
+  <si>
+    <t>KakaoTalk_20260722_192143008_01.jpg</t>
+  </si>
+  <si>
+    <t>18:52</t>
+  </si>
+  <si>
+    <t>329° NW</t>
   </si>
   <si>
     <r>
@@ -180,54 +180,51 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1219-405</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">KakaoTalk_20260722_192143008_02.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49° NE</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">주소 오버레이 없음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">KakaoTalk_20260722_192143008_03.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214° SW</t>
+        <family val="2"/>
+      </rPr>
+      <t>1219-405</t>
+    </r>
+  </si>
+  <si>
+    <t>KakaoTalk_20260722_192143008_02.jpg</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>49° NE</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>주소 오버레이 없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>KakaoTalk_20260722_192143008_03.jpg</t>
+  </si>
+  <si>
+    <t>214° SW</t>
   </si>
   <si>
     <r>
@@ -242,20 +239,19 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">765-4</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">KakaoTalk_20260722_192143008_04.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7° N</t>
+        <family val="2"/>
+      </rPr>
+      <t>765-4</t>
+    </r>
+  </si>
+  <si>
+    <t>KakaoTalk_20260722_192143008_04.jpg</t>
+  </si>
+  <si>
+    <t>18:46</t>
+  </si>
+  <si>
+    <t>7° N</t>
   </si>
   <si>
     <r>
@@ -270,22 +266,20 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">42</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">이 파일에 대한 참고사항</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
+        <family val="2"/>
+      </rPr>
+      <t>42</t>
+    </r>
+  </si>
+  <si>
+    <t>이 파일에 대한 참고사항</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">1. </t>
     </r>
@@ -295,31 +289,29 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">위도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">경도는 사진 앱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
+      <t>위도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>경도는 사진 앱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">(GPS Map Camera </t>
     </r>
@@ -329,16 +321,15 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">등</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
+      <t>등</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
     </r>
     <r>
       <rPr>
@@ -352,36 +343,33 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">OCR/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">육안 판독하여 추출한 값입니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
+        <family val="2"/>
+      </rPr>
+      <t>OCR/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>육안 판독하여 추출한 값입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">2. EXIF </t>
     </r>
@@ -397,8 +385,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">GPS </t>
     </r>
@@ -408,14 +395,13 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">태그와는 별개이며</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
+      <t>태그와는 별개이며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">, </t>
     </r>
@@ -425,59 +411,55 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">오버레이 텍스트 판독 결과이므로 소수 넷째 자리 이하 오차가 있을 수 있습니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3. 3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">번</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">연번</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
+      <t>오버레이 텍스트 판독 결과이므로 소수 넷째 자리 이하 오차가 있을 수 있습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3. 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>연번</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">) </t>
     </r>
@@ -493,8 +475,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">- </t>
     </r>
@@ -504,25 +485,23 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">임의로 채워넣지 않았습니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
+      <t>임의로 채워넣지 않았습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">4. </t>
     </r>
@@ -532,14 +511,13 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">실제 서비스에서는 사진 대량 업로드 시 이 과정을 자동화</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
+      <t>실제 서비스에서는 사진 대량 업로드 시 이 과정을 자동화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">(OCR </t>
     </r>
@@ -549,31 +527,29 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">파이프라인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">하는 것이 목표이며</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
+      <t>파이프라인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>하는 것이 목표이며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">, </t>
     </r>
@@ -583,27 +559,23 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">이 파일은 그 결과물의 예시입니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
+      <t>이 파일은 그 결과물의 예시입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
     </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="11">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -612,40 +584,23 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -653,7 +608,7 @@
       <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="12"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
@@ -661,13 +616,18 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="3">
@@ -685,7 +645,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -693,65 +653,29 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -810,47 +734,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -858,12 +798,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -892,7 +832,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -913,7 +853,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -964,7 +904,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -982,33 +922,32 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="34"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="8" max="8" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1034,8 +973,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+    <row r="2" spans="1:8">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1047,11 +986,11 @@
       <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>37.3955</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>126.9138</v>
+      <c r="E2" s="2">
+        <v>37.395499999999998</v>
+      </c>
+      <c r="F2" s="2">
+        <v>126.91379999999999</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>11</v>
@@ -1060,8 +999,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+    <row r="3" spans="1:8">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -1073,10 +1012,10 @@
       <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>37.3952</v>
-      </c>
-      <c r="F3" s="2" t="n">
+      <c r="E3" s="2">
+        <v>37.395200000000003</v>
+      </c>
+      <c r="F3" s="2">
         <v>126.913</v>
       </c>
       <c r="G3" s="2" t="s">
@@ -1086,8 +1025,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+    <row r="4" spans="1:8">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1099,10 +1038,10 @@
       <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>37.3948</v>
-      </c>
-      <c r="F4" s="2" t="n">
+      <c r="E4" s="2">
+        <v>37.394799999999996</v>
+      </c>
+      <c r="F4" s="2">
         <v>126.913</v>
       </c>
       <c r="G4" s="2" t="s">
@@ -1112,8 +1051,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+    <row r="5" spans="1:8">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -1125,10 +1064,10 @@
       <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>37.3948</v>
-      </c>
-      <c r="F5" s="2" t="n">
+      <c r="E5" s="2">
+        <v>37.394799999999996</v>
+      </c>
+      <c r="F5" s="2">
         <v>126.913</v>
       </c>
       <c r="G5" s="2" t="s">
@@ -1138,8 +1077,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+    <row r="6" spans="1:8">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -1151,10 +1090,10 @@
       <c r="D6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>37.3938</v>
-      </c>
-      <c r="F6" s="2" t="n">
+      <c r="E6" s="2">
+        <v>37.393799999999999</v>
+      </c>
+      <c r="F6" s="2">
         <v>126.9135</v>
       </c>
       <c r="G6" s="2" t="s">
@@ -1164,63 +1103,66 @@
         <v>27</v>
       </c>
     </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="C7" s="6">
+        <v>46260</v>
+      </c>
+      <c r="E7">
+        <v>37.395000000000003</v>
+      </c>
+      <c r="F7">
+        <v>126.913</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
+    <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:1" ht="15.75">
       <c r="A1" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:1">
       <c r="A2" s="5"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:1">
       <c r="A3" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:1">
       <c r="A4" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:1">
       <c r="A5" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:1">
       <c r="A6" s="5" t="s">
         <v>32</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/community_mapping_photo_list.xlsx
+++ b/community_mapping_photo_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AY CM code\anyang-community-map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4644D5-5E85-44C0-B185-F0EFDE965A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32FDAF3D-23EC-423B-B694-1D461FB159F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3525" yWindow="1860" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="커뮤니티매핑_사진목록" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
   <si>
     <t>연번</t>
   </si>
@@ -569,13 +569,88 @@
       </rPr>
       <t>.</t>
     </r>
+  </si>
+  <si>
+    <t>281° W</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>경기도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안양시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>만안구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장내로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 50</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -629,6 +704,18 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -656,7 +743,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -670,6 +757,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1103,7 +1193,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" ht="16.5">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1111,10 +1201,16 @@
         <v>46260</v>
       </c>
       <c r="E7">
-        <v>37.395000000000003</v>
+        <v>37.393700000000003</v>
       </c>
       <c r="F7">
-        <v>126.913</v>
+        <v>126.9143</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/community_mapping_photo_list.xlsx
+++ b/community_mapping_photo_list.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H230"/>
+  <dimension ref="A1:I230"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -425,6 +425,9 @@
       <c r="H1" t="str">
         <v>주소(오버레이 텍스트)</v>
       </c>
+      <c r="I1" t="str">
+        <v>패들렛댓글</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -451,6 +454,9 @@
       <c r="H2" t="str">
         <v>경기도 안양시 만안구 안양동 1219-515</v>
       </c>
+      <c r="I2" t="str">
+        <v>가드레일 부재</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -477,6 +483,9 @@
       <c r="H3" t="str">
         <v>경기도 안양시 만안구 안양동 1219-405</v>
       </c>
+      <c r="I3" t="str">
+        <v>좁은 인도</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -503,6 +512,9 @@
       <c r="H4" t="str">
         <v>(주소 오버레이 없음)</v>
       </c>
+      <c r="I4" t="str">
+        <v>정리된 인도의 좋은 사례</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -529,6 +541,9 @@
       <c r="H5" t="str">
         <v>경기도 안양시 만안구 안양동 765-4</v>
       </c>
+      <c r="I5" t="str">
+        <v>가드레일 부재</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -555,6 +570,9 @@
       <c r="H6" t="str">
         <v>경기도 안양시 만안구 장내로 42</v>
       </c>
+      <c r="I6" t="str">
+        <v>자연적인 감시성의 부재</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -575,6 +593,9 @@
       <c r="H7" t="str">
         <v>경기도 안양시 만안구 장내로 50</v>
       </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -601,6 +622,9 @@
       <c r="H8" t="str">
         <v/>
       </c>
+      <c r="I8" t="str">
+        <v>비탈길 안전망 설치</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -627,6 +651,9 @@
       <c r="H9" t="str">
         <v/>
       </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -653,6 +680,9 @@
       <c r="H10" t="str">
         <v/>
       </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -679,6 +709,9 @@
       <c r="H11" t="str">
         <v/>
       </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -705,6 +738,9 @@
       <c r="H12" t="str">
         <v/>
       </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -731,6 +767,9 @@
       <c r="H13" t="str">
         <v/>
       </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -757,6 +796,9 @@
       <c r="H14" t="str">
         <v/>
       </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -783,6 +825,9 @@
       <c r="H15" t="str">
         <v/>
       </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -809,6 +854,9 @@
       <c r="H16" t="str">
         <v/>
       </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -835,6 +883,9 @@
       <c r="H17" t="str">
         <v/>
       </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -861,6 +912,9 @@
       <c r="H18" t="str">
         <v/>
       </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -887,6 +941,9 @@
       <c r="H19" t="str">
         <v/>
       </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -913,6 +970,9 @@
       <c r="H20" t="str">
         <v/>
       </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -939,6 +999,9 @@
       <c r="H21" t="str">
         <v/>
       </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -965,6 +1028,9 @@
       <c r="H22" t="str">
         <v/>
       </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -991,6 +1057,9 @@
       <c r="H23" t="str">
         <v/>
       </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -1017,6 +1086,9 @@
       <c r="H24" t="str">
         <v/>
       </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -1043,6 +1115,9 @@
       <c r="H25" t="str">
         <v/>
       </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -1069,6 +1144,9 @@
       <c r="H26" t="str">
         <v/>
       </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -1095,6 +1173,9 @@
       <c r="H27" t="str">
         <v/>
       </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -1121,6 +1202,9 @@
       <c r="H28" t="str">
         <v/>
       </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -1147,6 +1231,9 @@
       <c r="H29" t="str">
         <v/>
       </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -1173,6 +1260,9 @@
       <c r="H30" t="str">
         <v/>
       </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -1199,6 +1289,9 @@
       <c r="H31" t="str">
         <v/>
       </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -1225,6 +1318,9 @@
       <c r="H32" t="str">
         <v/>
       </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -1251,6 +1347,9 @@
       <c r="H33" t="str">
         <v/>
       </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -1277,6 +1376,9 @@
       <c r="H34" t="str">
         <v/>
       </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -1303,6 +1405,9 @@
       <c r="H35" t="str">
         <v/>
       </c>
+      <c r="I35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -1329,6 +1434,9 @@
       <c r="H36" t="str">
         <v/>
       </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -1355,6 +1463,9 @@
       <c r="H37" t="str">
         <v/>
       </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -1381,6 +1492,9 @@
       <c r="H38" t="str">
         <v/>
       </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -1407,6 +1521,9 @@
       <c r="H39" t="str">
         <v/>
       </c>
+      <c r="I39" t="str">
+        <v>쓰레기 정리</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -1433,6 +1550,9 @@
       <c r="H40" t="str">
         <v/>
       </c>
+      <c r="I40" t="str">
+        <v>전지작업 필요</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -1459,6 +1579,9 @@
       <c r="H41" t="str">
         <v/>
       </c>
+      <c r="I41" t="str">
+        <v>공간활용</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -1485,6 +1608,9 @@
       <c r="H42" t="str">
         <v/>
       </c>
+      <c r="I42" t="str">
+        <v>급한 계단</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -1511,6 +1637,9 @@
       <c r="H43" t="str">
         <v/>
       </c>
+      <c r="I43" t="str">
+        <v>쓰레기 정리</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -1537,6 +1666,9 @@
       <c r="H44" t="str">
         <v/>
       </c>
+      <c r="I44" t="str">
+        <v>계단 안전시설 설치 요망</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -1563,6 +1695,9 @@
       <c r="H45" t="str">
         <v/>
       </c>
+      <c r="I45" t="str">
+        <v>도시미관 정비필요</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -1589,6 +1724,9 @@
       <c r="H46" t="str">
         <v/>
       </c>
+      <c r="I46" t="str">
+        <v>추락위험</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -1615,6 +1753,9 @@
       <c r="H47" t="str">
         <v/>
       </c>
+      <c r="I47" t="str">
+        <v>감시성 부재</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -1641,6 +1782,9 @@
       <c r="H48" t="str">
         <v/>
       </c>
+      <c r="I48" t="str">
+        <v>쓰레기 정리</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -1667,6 +1811,9 @@
       <c r="H49" t="str">
         <v/>
       </c>
+      <c r="I49" t="str">
+        <v>미관 정리 필요</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -1693,6 +1840,9 @@
       <c r="H50" t="str">
         <v/>
       </c>
+      <c r="I50" t="str">
+        <v>공간활용</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -1719,6 +1869,9 @@
       <c r="H51" t="str">
         <v/>
       </c>
+      <c r="I51" t="str">
+        <v>도시미관 정리필요</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -1745,6 +1898,9 @@
       <c r="H52" t="str">
         <v/>
       </c>
+      <c r="I52" t="str">
+        <v>추락 위험</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -1771,6 +1927,9 @@
       <c r="H53" t="str">
         <v/>
       </c>
+      <c r="I53" t="str">
+        <v>보행자를 위한 통로 부재</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -1797,6 +1956,9 @@
       <c r="H54" t="str">
         <v/>
       </c>
+      <c r="I54" t="str">
+        <v>혼잡한 5거리 정리필요</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -1823,6 +1985,9 @@
       <c r="H55" t="str">
         <v/>
       </c>
+      <c r="I55" t="str">
+        <v>조명시설 설치 필요</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -1849,6 +2014,9 @@
       <c r="H56" t="str">
         <v/>
       </c>
+      <c r="I56" t="str">
+        <v>쓰레기 정리</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -1875,6 +2043,9 @@
       <c r="H57" t="str">
         <v/>
       </c>
+      <c r="I57" t="str">
+        <v>돌출된 인도</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -1901,6 +2072,9 @@
       <c r="H58" t="str">
         <v/>
       </c>
+      <c r="I58" t="str">
+        <v>도시미관 정리필요</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -1927,6 +2101,9 @@
       <c r="H59" t="str">
         <v/>
       </c>
+      <c r="I59" t="str">
+        <v>부서진 인도</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -1953,6 +2130,9 @@
       <c r="H60" t="str">
         <v/>
       </c>
+      <c r="I60" t="str">
+        <v>보행자와 분리 필요</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -1979,6 +2159,9 @@
       <c r="H61" t="str">
         <v/>
       </c>
+      <c r="I61" t="str">
+        <v>돌출된 도로</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -2005,6 +2188,9 @@
       <c r="H62" t="str">
         <v/>
       </c>
+      <c r="I62" t="str">
+        <v>가드레일 필요</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -2031,6 +2217,9 @@
       <c r="H63" t="str">
         <v/>
       </c>
+      <c r="I63" t="str">
+        <v>가드레일 부재</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -2057,6 +2246,9 @@
       <c r="H64" t="str">
         <v/>
       </c>
+      <c r="I64" t="str">
+        <v>경사진 도로</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65">
@@ -2083,6 +2275,9 @@
       <c r="H65" t="str">
         <v/>
       </c>
+      <c r="I65" t="str">
+        <v>추락위험</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66">
@@ -2109,6 +2304,9 @@
       <c r="H66" t="str">
         <v/>
       </c>
+      <c r="I66" t="str">
+        <v>계단에 가드레일 설치</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67">
@@ -2135,6 +2333,9 @@
       <c r="H67" t="str">
         <v/>
       </c>
+      <c r="I67" t="str">
+        <v>축대 정리</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68">
@@ -2161,6 +2362,9 @@
       <c r="H68" t="str">
         <v/>
       </c>
+      <c r="I68" t="str">
+        <v>보행자를 위한 안전시설 설치 필요</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69">
@@ -2187,6 +2391,9 @@
       <c r="H69" t="str">
         <v/>
       </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70">
@@ -2213,6 +2420,9 @@
       <c r="H70" t="str">
         <v/>
       </c>
+      <c r="I70" t="str">
+        <v>하수구 뚜껑이 잘 안맞고그 위에 각종 돌 맹이등을 올려놓아 통행에 불편을 야기합니더</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71">
@@ -2239,6 +2449,9 @@
       <c r="H71" t="str">
         <v/>
       </c>
+      <c r="I71" t="str">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72">
@@ -2265,6 +2478,9 @@
       <c r="H72" t="str">
         <v/>
       </c>
+      <c r="I72" t="str">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73">
@@ -2291,6 +2507,9 @@
       <c r="H73" t="str">
         <v/>
       </c>
+      <c r="I73" t="str">
+        <v>통행로에 많은 물건들로통행어 불편을~~</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74">
@@ -2317,6 +2536,9 @@
       <c r="H74" t="str">
         <v/>
       </c>
+      <c r="I74" t="str">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75">
@@ -2343,6 +2565,9 @@
       <c r="H75" t="str">
         <v/>
       </c>
+      <c r="I75" t="str">
+        <v>노후담장 관리</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76">
@@ -2369,6 +2594,9 @@
       <c r="H76" t="str">
         <v/>
       </c>
+      <c r="I76" t="str">
+        <v>골목쓰레기 방치</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77">
@@ -2395,6 +2623,9 @@
       <c r="H77" t="str">
         <v/>
       </c>
+      <c r="I77" t="str">
+        <v>장마대비 담장관리</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78">
@@ -2421,6 +2652,9 @@
       <c r="H78" t="str">
         <v/>
       </c>
+      <c r="I78" t="str">
+        <v>환경개선</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79">
@@ -2447,6 +2681,9 @@
       <c r="H79" t="str">
         <v/>
       </c>
+      <c r="I79" t="str">
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80">
@@ -2473,6 +2710,9 @@
       <c r="H80" t="str">
         <v/>
       </c>
+      <c r="I80" t="str">
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81">
@@ -2499,6 +2739,9 @@
       <c r="H81" t="str">
         <v/>
       </c>
+      <c r="I81" t="str">
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82">
@@ -2525,6 +2768,9 @@
       <c r="H82" t="str">
         <v/>
       </c>
+      <c r="I82" t="str">
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83">
@@ -2551,6 +2797,9 @@
       <c r="H83" t="str">
         <v/>
       </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84">
@@ -2577,6 +2826,9 @@
       <c r="H84" t="str">
         <v/>
       </c>
+      <c r="I84" t="str">
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85">
@@ -2603,6 +2855,9 @@
       <c r="H85" t="str">
         <v/>
       </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86">
@@ -2629,6 +2884,9 @@
       <c r="H86" t="str">
         <v/>
       </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87">
@@ -2655,6 +2913,9 @@
       <c r="H87" t="str">
         <v/>
       </c>
+      <c r="I87" t="str">
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88">
@@ -2681,6 +2942,9 @@
       <c r="H88" t="str">
         <v/>
       </c>
+      <c r="I88" t="str">
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89">
@@ -2707,6 +2971,9 @@
       <c r="H89" t="str">
         <v/>
       </c>
+      <c r="I89" t="str">
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90">
@@ -2733,6 +3000,9 @@
       <c r="H90" t="str">
         <v/>
       </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91">
@@ -2759,6 +3029,9 @@
       <c r="H91" t="str">
         <v/>
       </c>
+      <c r="I91" t="str">
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92">
@@ -2785,6 +3058,9 @@
       <c r="H92" t="str">
         <v/>
       </c>
+      <c r="I92" t="str">
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93">
@@ -2811,6 +3087,9 @@
       <c r="H93" t="str">
         <v/>
       </c>
+      <c r="I93" t="str">
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94">
@@ -2837,6 +3116,9 @@
       <c r="H94" t="str">
         <v/>
       </c>
+      <c r="I94" t="str">
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95">
@@ -2863,6 +3145,9 @@
       <c r="H95" t="str">
         <v/>
       </c>
+      <c r="I95" t="str">
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96">
@@ -2889,6 +3174,9 @@
       <c r="H96" t="str">
         <v/>
       </c>
+      <c r="I96" t="str">
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97">
@@ -2915,6 +3203,9 @@
       <c r="H97" t="str">
         <v/>
       </c>
+      <c r="I97" t="str">
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98">
@@ -2941,6 +3232,9 @@
       <c r="H98" t="str">
         <v/>
       </c>
+      <c r="I98" t="str">
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99">
@@ -2967,6 +3261,9 @@
       <c r="H99" t="str">
         <v/>
       </c>
+      <c r="I99" t="str">
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100">
@@ -2993,6 +3290,9 @@
       <c r="H100" t="str">
         <v/>
       </c>
+      <c r="I100" t="str">
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101">
@@ -3019,6 +3319,9 @@
       <c r="H101" t="str">
         <v/>
       </c>
+      <c r="I101" t="str">
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102">
@@ -3045,6 +3348,9 @@
       <c r="H102" t="str">
         <v/>
       </c>
+      <c r="I102" t="str">
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103">
@@ -3071,6 +3377,9 @@
       <c r="H103" t="str">
         <v/>
       </c>
+      <c r="I103" t="str">
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104">
@@ -3097,6 +3406,9 @@
       <c r="H104" t="str">
         <v/>
       </c>
+      <c r="I104" t="str">
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105">
@@ -3123,6 +3435,9 @@
       <c r="H105" t="str">
         <v/>
       </c>
+      <c r="I105" t="str">
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106">
@@ -3149,6 +3464,9 @@
       <c r="H106" t="str">
         <v/>
       </c>
+      <c r="I106" t="str">
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107">
@@ -3175,6 +3493,9 @@
       <c r="H107" t="str">
         <v/>
       </c>
+      <c r="I107" t="str">
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108">
@@ -3201,6 +3522,9 @@
       <c r="H108" t="str">
         <v/>
       </c>
+      <c r="I108" t="str">
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109">
@@ -3227,6 +3551,9 @@
       <c r="H109" t="str">
         <v/>
       </c>
+      <c r="I109" t="str">
+        <v>종량제봉투사용해야하는데  도로가쓰레기그냥버려서 보기가 넘 안좋아요</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110">
@@ -3253,6 +3580,9 @@
       <c r="H110" t="str">
         <v/>
       </c>
+      <c r="I110" t="str">
+        <v>사람이 살고있는데 통행에 넘 위험에보입니다</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111">
@@ -3279,6 +3609,9 @@
       <c r="H111" t="str">
         <v/>
       </c>
+      <c r="I111" t="str">
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112">
@@ -3305,6 +3638,9 @@
       <c r="H112" t="str">
         <v/>
       </c>
+      <c r="I112" t="str">
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113">
@@ -3331,6 +3667,9 @@
       <c r="H113" t="str">
         <v/>
       </c>
+      <c r="I113" t="str">
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114">
@@ -3357,6 +3696,9 @@
       <c r="H114" t="str">
         <v/>
       </c>
+      <c r="I114" t="str">
+        <v>주민분들이새로된길이  비가오던지눈이오면  미끄러워서 다치고위험하다고하네요</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115">
@@ -3383,6 +3725,9 @@
       <c r="H115" t="str">
         <v/>
       </c>
+      <c r="I115" t="str">
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116">
@@ -3409,6 +3754,9 @@
       <c r="H116" t="str">
         <v/>
       </c>
+      <c r="I116" t="str">
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117">
@@ -3435,6 +3783,9 @@
       <c r="H117" t="str">
         <v/>
       </c>
+      <c r="I117" t="str">
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118">
@@ -3461,6 +3812,9 @@
       <c r="H118" t="str">
         <v/>
       </c>
+      <c r="I118" t="str">
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119">
@@ -3487,6 +3841,9 @@
       <c r="H119" t="str">
         <v/>
       </c>
+      <c r="I119" t="str">
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120">
@@ -3513,6 +3870,9 @@
       <c r="H120" t="str">
         <v/>
       </c>
+      <c r="I120" t="str">
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121">
@@ -3539,6 +3899,9 @@
       <c r="H121" t="str">
         <v/>
       </c>
+      <c r="I121" t="str">
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122">
@@ -3565,6 +3928,9 @@
       <c r="H122" t="str">
         <v/>
       </c>
+      <c r="I122" t="str">
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123">
@@ -3591,6 +3957,9 @@
       <c r="H123" t="str">
         <v/>
       </c>
+      <c r="I123" t="str">
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124">
@@ -3617,6 +3986,9 @@
       <c r="H124" t="str">
         <v/>
       </c>
+      <c r="I124" t="str">
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125">
@@ -3643,6 +4015,9 @@
       <c r="H125" t="str">
         <v/>
       </c>
+      <c r="I125" t="str">
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126">
@@ -3669,6 +4044,9 @@
       <c r="H126" t="str">
         <v/>
       </c>
+      <c r="I126" t="str">
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127">
@@ -3695,6 +4073,9 @@
       <c r="H127" t="str">
         <v/>
       </c>
+      <c r="I127" t="str">
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128">
@@ -3721,6 +4102,9 @@
       <c r="H128" t="str">
         <v/>
       </c>
+      <c r="I128" t="str">
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129">
@@ -3747,6 +4131,9 @@
       <c r="H129" t="str">
         <v/>
       </c>
+      <c r="I129" t="str">
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130">
@@ -3773,6 +4160,9 @@
       <c r="H130" t="str">
         <v/>
       </c>
+      <c r="I130" t="str">
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131">
@@ -3799,6 +4189,9 @@
       <c r="H131" t="str">
         <v/>
       </c>
+      <c r="I131" t="str">
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132">
@@ -3825,6 +4218,9 @@
       <c r="H132" t="str">
         <v/>
       </c>
+      <c r="I132" t="str">
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133">
@@ -3851,6 +4247,9 @@
       <c r="H133" t="str">
         <v/>
       </c>
+      <c r="I133" t="str">
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134">
@@ -3877,6 +4276,9 @@
       <c r="H134" t="str">
         <v/>
       </c>
+      <c r="I134" t="str">
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135">
@@ -3903,6 +4305,9 @@
       <c r="H135" t="str">
         <v/>
       </c>
+      <c r="I135" t="str">
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136">
@@ -3929,6 +4334,9 @@
       <c r="H136" t="str">
         <v/>
       </c>
+      <c r="I136" t="str">
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137">
@@ -3955,6 +4363,9 @@
       <c r="H137" t="str">
         <v/>
       </c>
+      <c r="I137" t="str">
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138">
@@ -3981,6 +4392,9 @@
       <c r="H138" t="str">
         <v/>
       </c>
+      <c r="I138" t="str">
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139">
@@ -4007,6 +4421,9 @@
       <c r="H139" t="str">
         <v/>
       </c>
+      <c r="I139" t="str">
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140">
@@ -4033,6 +4450,9 @@
       <c r="H140" t="str">
         <v/>
       </c>
+      <c r="I140" t="str">
+        <v>가드레일 부재</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141">
@@ -4059,6 +4479,9 @@
       <c r="H141" t="str">
         <v/>
       </c>
+      <c r="I141" t="str">
+        <v>자연적인 감시성 부재</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142">
@@ -4085,6 +4508,9 @@
       <c r="H142" t="str">
         <v/>
       </c>
+      <c r="I142" t="str">
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143">
@@ -4111,6 +4537,9 @@
       <c r="H143" t="str">
         <v/>
       </c>
+      <c r="I143" t="str">
+        <v>좌우 가드레일의 차이?</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144">
@@ -4137,6 +4566,9 @@
       <c r="H144" t="str">
         <v/>
       </c>
+      <c r="I144" t="str">
+        <v>형식적인 가드레일</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145">
@@ -4163,6 +4595,9 @@
       <c r="H145" t="str">
         <v/>
       </c>
+      <c r="I145" t="str">
+        <v>미관 정리필요</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146">
@@ -4189,6 +4624,9 @@
       <c r="H146" t="str">
         <v/>
       </c>
+      <c r="I146" t="str">
+        <v>가드레일 부재</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147">
@@ -4215,6 +4653,9 @@
       <c r="H147" t="str">
         <v/>
       </c>
+      <c r="I147" t="str">
+        <v>좁은 인도</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148">
@@ -4241,6 +4682,9 @@
       <c r="H148" t="str">
         <v/>
       </c>
+      <c r="I148" t="str">
+        <v>정리된 인도의 좋은 사례</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149">
@@ -4267,6 +4711,9 @@
       <c r="H149" t="str">
         <v/>
       </c>
+      <c r="I149" t="str">
+        <v>가드레일 부재</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150">
@@ -4293,6 +4740,9 @@
       <c r="H150" t="str">
         <v/>
       </c>
+      <c r="I150" t="str">
+        <v>자연적인 감시성의 부재</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151">
@@ -4319,6 +4769,9 @@
       <c r="H151" t="str">
         <v/>
       </c>
+      <c r="I151" t="str">
+        <v>좁은 보행통로</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152">
@@ -4345,6 +4798,9 @@
       <c r="H152" t="str">
         <v/>
       </c>
+      <c r="I152" t="str">
+        <v>쓰레기 정리</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153">
@@ -4371,6 +4827,9 @@
       <c r="H153" t="str">
         <v/>
       </c>
+      <c r="I153" t="str">
+        <v>돌출된 인도</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154">
@@ -4397,6 +4856,9 @@
       <c r="H154" t="str">
         <v/>
       </c>
+      <c r="I154" t="str">
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155">
@@ -4423,6 +4885,9 @@
       <c r="H155" t="str">
         <v/>
       </c>
+      <c r="I155" t="str">
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156">
@@ -4449,6 +4914,9 @@
       <c r="H156" t="str">
         <v/>
       </c>
+      <c r="I156" t="str">
+        <v>식수 가로수 보호 블렁 올라와 걸려 넘어질 위험이 있음</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157">
@@ -4475,6 +4943,9 @@
       <c r="H157" t="str">
         <v/>
       </c>
+      <c r="I157" t="str">
+        <v>블럭 빠짐</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158">
@@ -4501,6 +4972,9 @@
       <c r="H158" t="str">
         <v/>
       </c>
+      <c r="I158" t="str">
+        <v>블럭 빠짐 위험</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159">
@@ -4527,6 +5001,9 @@
       <c r="H159" t="str">
         <v/>
       </c>
+      <c r="I159" t="str">
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160">
@@ -4553,6 +5030,9 @@
       <c r="H160" t="str">
         <v/>
       </c>
+      <c r="I160" t="str">
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161">
@@ -4579,6 +5059,9 @@
       <c r="H161" t="str">
         <v/>
       </c>
+      <c r="I161" t="str">
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162">
@@ -4605,6 +5088,9 @@
       <c r="H162" t="str">
         <v/>
       </c>
+      <c r="I162" t="str">
+        <v>많은 물건들이 적치돕</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163">
@@ -4631,6 +5117,9 @@
       <c r="H163" t="str">
         <v/>
       </c>
+      <c r="I163" t="str">
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164">
@@ -4657,6 +5146,9 @@
       <c r="H164" t="str">
         <v/>
       </c>
+      <c r="I164" t="str">
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165">
@@ -4683,6 +5175,9 @@
       <c r="H165" t="str">
         <v/>
       </c>
+      <c r="I165" t="str">
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166">
@@ -4709,6 +5204,9 @@
       <c r="H166" t="str">
         <v/>
       </c>
+      <c r="I166" t="str">
+        <v>건널목이 차도보다 낮아서 물이 고이면 물을 피해 차도로 걷다가 사고가 몇번  있었다고 함</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167">
@@ -4735,6 +5233,9 @@
       <c r="H167" t="str">
         <v/>
       </c>
+      <c r="I167" t="str">
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168">
@@ -4761,6 +5262,9 @@
       <c r="H168" t="str">
         <v/>
       </c>
+      <c r="I168" t="str">
+        <v>보도블럭 패임</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169">
@@ -4787,6 +5291,9 @@
       <c r="H169" t="str">
         <v/>
       </c>
+      <c r="I169" t="str">
+        <v>비탈길 방어막 설치</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170">
@@ -4813,6 +5320,9 @@
       <c r="H170" t="str">
         <v/>
       </c>
+      <c r="I170" t="str">
+        <v>비탈길 안전망 설치</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171">
@@ -4839,6 +5349,9 @@
       <c r="H171" t="str">
         <v/>
       </c>
+      <c r="I171" t="str">
+        <v>학교표시판 한곳으로</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172">
@@ -4865,6 +5378,9 @@
       <c r="H172" t="str">
         <v/>
       </c>
+      <c r="I172" t="str">
+        <v>언덕길 방어막 설치</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173">
@@ -4891,6 +5407,9 @@
       <c r="H173" t="str">
         <v/>
       </c>
+      <c r="I173" t="str">
+        <v>쓰레기통  신설</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174">
@@ -4917,6 +5436,9 @@
       <c r="H174" t="str">
         <v/>
       </c>
+      <c r="I174" t="str">
+        <v>골목길 표시판 설치</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175">
@@ -4943,6 +5465,9 @@
       <c r="H175" t="str">
         <v/>
       </c>
+      <c r="I175" t="str">
+        <v>위험 축대 관리 표시판설치</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176">
@@ -4969,6 +5494,9 @@
       <c r="H176" t="str">
         <v/>
       </c>
+      <c r="I176" t="str">
+        <v>골목길 가로등 설치</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177">
@@ -4995,6 +5523,9 @@
       <c r="H177" t="str">
         <v/>
       </c>
+      <c r="I177" t="str">
+        <v>위험 축대 표시</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178">
@@ -5021,6 +5552,9 @@
       <c r="H178" t="str">
         <v/>
       </c>
+      <c r="I178" t="str">
+        <v>설치한지 얼마안되지만 이걸로 여름에는  빗길에  겨울에는 눈길에 미끄러지는 경우가 종종 있다고 하니 미끄럼방지 같은 후속조치가 필요함</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179">
@@ -5047,6 +5581,9 @@
       <c r="H179" t="str">
         <v/>
       </c>
+      <c r="I179" t="str">
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180">
@@ -5073,6 +5610,9 @@
       <c r="H180" t="str">
         <v/>
       </c>
+      <c r="I180" t="str">
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181">
@@ -5099,6 +5639,9 @@
       <c r="H181" t="str">
         <v/>
       </c>
+      <c r="I181" t="str">
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182">
@@ -5125,6 +5668,9 @@
       <c r="H182" t="str">
         <v/>
       </c>
+      <c r="I182" t="str">
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183">
@@ -5151,6 +5697,9 @@
       <c r="H183" t="str">
         <v/>
       </c>
+      <c r="I183" t="str">
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184">
@@ -5177,6 +5726,9 @@
       <c r="H184" t="str">
         <v/>
       </c>
+      <c r="I184" t="str">
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185">
@@ -5203,6 +5755,9 @@
       <c r="H185" t="str">
         <v/>
       </c>
+      <c r="I185" t="str">
+        <v>상당히 높은지역이기도 하고 좁은길이기에 너무 위험해 보임.. 길가에 야간등 장치 필요해 보임</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186">
@@ -5229,6 +5784,9 @@
       <c r="H186" t="str">
         <v/>
       </c>
+      <c r="I186" t="str">
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187">
@@ -5255,6 +5813,9 @@
       <c r="H187" t="str">
         <v/>
       </c>
+      <c r="I187" t="str">
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188">
@@ -5281,6 +5842,9 @@
       <c r="H188" t="str">
         <v/>
       </c>
+      <c r="I188" t="str">
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189">
@@ -5307,6 +5871,9 @@
       <c r="H189" t="str">
         <v/>
       </c>
+      <c r="I189" t="str">
+        <v>갈라진 보도블럭</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190">
@@ -5333,6 +5900,9 @@
       <c r="H190" t="str">
         <v/>
       </c>
+      <c r="I190" t="str">
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191">
@@ -5359,6 +5929,9 @@
       <c r="H191" t="str">
         <v/>
       </c>
+      <c r="I191" t="str">
+        <v>경사진 곳이여서 상당히 위험해 보임.. 보도블럭 교체와 야간에 위험해 보임 - 바닥에 야간등을 설치해야 할듯합니다</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192">
@@ -5385,6 +5958,9 @@
       <c r="H192" t="str">
         <v/>
       </c>
+      <c r="I192" t="str">
+        <v>우리동네에 이런지역이?? 이지역에 살면서도 다시금 놀랍네요..</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193">
@@ -5411,6 +5987,9 @@
       <c r="H193" t="str">
         <v/>
       </c>
+      <c r="I193" t="str">
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194">
@@ -5437,6 +6016,9 @@
       <c r="H194" t="str">
         <v/>
       </c>
+      <c r="I194" t="str">
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195">
@@ -5463,6 +6045,9 @@
       <c r="H195" t="str">
         <v/>
       </c>
+      <c r="I195" t="str">
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196">
@@ -5489,6 +6074,9 @@
       <c r="H196" t="str">
         <v/>
       </c>
+      <c r="I196" t="str">
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197">
@@ -5515,6 +6103,9 @@
       <c r="H197" t="str">
         <v/>
       </c>
+      <c r="I197" t="str">
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198">
@@ -5541,6 +6132,9 @@
       <c r="H198" t="str">
         <v/>
       </c>
+      <c r="I198" t="str">
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199">
@@ -5567,6 +6161,9 @@
       <c r="H199" t="str">
         <v/>
       </c>
+      <c r="I199" t="str">
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200">
@@ -5593,6 +6190,9 @@
       <c r="H200" t="str">
         <v/>
       </c>
+      <c r="I200" t="str">
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201">
@@ -5619,6 +6219,9 @@
       <c r="H201" t="str">
         <v/>
       </c>
+      <c r="I201" t="str">
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202">
@@ -5645,6 +6248,9 @@
       <c r="H202" t="str">
         <v/>
       </c>
+      <c r="I202" t="str">
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203">
@@ -5671,6 +6277,9 @@
       <c r="H203" t="str">
         <v/>
       </c>
+      <c r="I203" t="str">
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204">
@@ -5697,6 +6306,9 @@
       <c r="H204" t="str">
         <v/>
       </c>
+      <c r="I204" t="str">
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="A205">
@@ -5723,6 +6335,9 @@
       <c r="H205" t="str">
         <v/>
       </c>
+      <c r="I205" t="str">
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206">
@@ -5749,6 +6364,9 @@
       <c r="H206" t="str">
         <v/>
       </c>
+      <c r="I206" t="str">
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="A207">
@@ -5775,6 +6393,9 @@
       <c r="H207" t="str">
         <v/>
       </c>
+      <c r="I207" t="str">
+        <v/>
+      </c>
     </row>
     <row r="208">
       <c r="A208">
@@ -5801,6 +6422,9 @@
       <c r="H208" t="str">
         <v/>
       </c>
+      <c r="I208" t="str">
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="A209">
@@ -5827,6 +6451,9 @@
       <c r="H209" t="str">
         <v/>
       </c>
+      <c r="I209" t="str">
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="A210">
@@ -5853,6 +6480,9 @@
       <c r="H210" t="str">
         <v/>
       </c>
+      <c r="I210" t="str">
+        <v>이쪽은 사유지라서 안되어 있는건지?</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211">
@@ -5879,6 +6509,9 @@
       <c r="H211" t="str">
         <v/>
       </c>
+      <c r="I211" t="str">
+        <v/>
+      </c>
     </row>
     <row r="212">
       <c r="A212">
@@ -5905,6 +6538,9 @@
       <c r="H212" t="str">
         <v/>
       </c>
+      <c r="I212" t="str">
+        <v/>
+      </c>
     </row>
     <row r="213">
       <c r="A213">
@@ -5931,6 +6567,9 @@
       <c r="H213" t="str">
         <v/>
       </c>
+      <c r="I213" t="str">
+        <v/>
+      </c>
     </row>
     <row r="214">
       <c r="A214">
@@ -5957,6 +6596,9 @@
       <c r="H214" t="str">
         <v/>
       </c>
+      <c r="I214" t="str">
+        <v/>
+      </c>
     </row>
     <row r="215">
       <c r="A215">
@@ -5983,6 +6625,9 @@
       <c r="H215" t="str">
         <v/>
       </c>
+      <c r="I215" t="str">
+        <v/>
+      </c>
     </row>
     <row r="216">
       <c r="A216">
@@ -6009,6 +6654,9 @@
       <c r="H216" t="str">
         <v/>
       </c>
+      <c r="I216" t="str">
+        <v/>
+      </c>
     </row>
     <row r="217">
       <c r="A217">
@@ -6035,6 +6683,9 @@
       <c r="H217" t="str">
         <v/>
       </c>
+      <c r="I217" t="str">
+        <v/>
+      </c>
     </row>
     <row r="218">
       <c r="A218">
@@ -6061,6 +6712,9 @@
       <c r="H218" t="str">
         <v/>
       </c>
+      <c r="I218" t="str">
+        <v/>
+      </c>
     </row>
     <row r="219">
       <c r="A219">
@@ -6087,6 +6741,9 @@
       <c r="H219" t="str">
         <v/>
       </c>
+      <c r="I219" t="str">
+        <v/>
+      </c>
     </row>
     <row r="220">
       <c r="A220">
@@ -6113,6 +6770,9 @@
       <c r="H220" t="str">
         <v/>
       </c>
+      <c r="I220" t="str">
+        <v/>
+      </c>
     </row>
     <row r="221">
       <c r="A221">
@@ -6139,6 +6799,9 @@
       <c r="H221" t="str">
         <v/>
       </c>
+      <c r="I221" t="str">
+        <v/>
+      </c>
     </row>
     <row r="222">
       <c r="A222">
@@ -6165,6 +6828,9 @@
       <c r="H222" t="str">
         <v/>
       </c>
+      <c r="I222" t="str">
+        <v/>
+      </c>
     </row>
     <row r="223">
       <c r="A223">
@@ -6191,6 +6857,9 @@
       <c r="H223" t="str">
         <v/>
       </c>
+      <c r="I223" t="str">
+        <v/>
+      </c>
     </row>
     <row r="224">
       <c r="A224">
@@ -6217,6 +6886,9 @@
       <c r="H224" t="str">
         <v/>
       </c>
+      <c r="I224" t="str">
+        <v/>
+      </c>
     </row>
     <row r="225">
       <c r="A225">
@@ -6243,6 +6915,9 @@
       <c r="H225" t="str">
         <v/>
       </c>
+      <c r="I225" t="str">
+        <v/>
+      </c>
     </row>
     <row r="226">
       <c r="A226">
@@ -6269,6 +6944,9 @@
       <c r="H226" t="str">
         <v/>
       </c>
+      <c r="I226" t="str">
+        <v/>
+      </c>
     </row>
     <row r="227">
       <c r="A227">
@@ -6295,6 +6973,9 @@
       <c r="H227" t="str">
         <v/>
       </c>
+      <c r="I227" t="str">
+        <v/>
+      </c>
     </row>
     <row r="228">
       <c r="A228">
@@ -6321,6 +7002,9 @@
       <c r="H228" t="str">
         <v/>
       </c>
+      <c r="I228" t="str">
+        <v/>
+      </c>
     </row>
     <row r="229">
       <c r="A229">
@@ -6347,6 +7031,9 @@
       <c r="H229" t="str">
         <v/>
       </c>
+      <c r="I229" t="str">
+        <v/>
+      </c>
     </row>
     <row r="230">
       <c r="A230">
@@ -6373,10 +7060,13 @@
       <c r="H230" t="str">
         <v/>
       </c>
+      <c r="I230" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H230"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I230"/>
   </ignoredErrors>
 </worksheet>
 </file>
